--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486939_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486939_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.3465</v>
+        <v>3.442</v>
       </c>
       <c r="E2" t="n">
-        <v>4.0145</v>
+        <v>4.0804</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.6681</v>
+        <v>-0.6384</v>
       </c>
       <c r="G2" t="n">
         <v>2.2307</v>
@@ -610,13 +610,13 @@
         <v>0.8214</v>
       </c>
       <c r="S2" t="n">
-        <v>0.6435</v>
+        <v>0.739</v>
       </c>
       <c r="T2" t="n">
-        <v>0.9258999999999999</v>
+        <v>0.9917</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.2824</v>
+        <v>-0.2527</v>
       </c>
       <c r="V2" t="n">
         <v>-0.3491</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8843</v>
+        <v>1.9788</v>
       </c>
       <c r="E3" t="n">
-        <v>2.978</v>
+        <v>3.7761</v>
       </c>
       <c r="F3" t="n">
-        <v>-2.0937</v>
+        <v>-1.7973</v>
       </c>
       <c r="G3" t="n">
         <v>0.4238</v>
@@ -688,13 +688,13 @@
         <v>1.6427</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.0849</v>
+        <v>0.0097</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.6355</v>
+        <v>0.1626</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.4493</v>
+        <v>-0.1529</v>
       </c>
       <c r="V3" t="n">
         <v>0.9294</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.1071</v>
+        <v>0.1523</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.7902</v>
+        <v>-0.6197</v>
       </c>
       <c r="F4" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.772</v>
       </c>
       <c r="G4" t="n">
         <v>0.0389</v>
@@ -766,13 +766,13 @@
         <v>0.2053</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.3514</v>
+        <v>-0.092</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.1317</v>
+        <v>0.0387</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.2197</v>
+        <v>-0.1307</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>E. COLL COMABELLA</t>
+          <t>N. FERRER IGLESIA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.4743</v>
+        <v>-1.6549</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.3894</v>
+        <v>-1.1072</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.0849</v>
+        <v>-0.5477</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.0984</v>
+        <v>-2.056</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.2723</v>
+        <v>-1.5245</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.8260999999999999</v>
+        <v>-0.5314</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.1994</v>
+        <v>-0.6304999999999999</v>
       </c>
       <c r="K5" t="n">
-        <v>1.1164</v>
+        <v>-0.0516</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.3158</v>
+        <v>-0.579</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.899</v>
+        <v>-1.4255</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.3887</v>
+        <v>-1.473</v>
       </c>
       <c r="O5" t="n">
-        <v>0.4897</v>
+        <v>0.0475</v>
       </c>
       <c r="P5" t="n">
-        <v>0.616</v>
+        <v>-0.4107</v>
       </c>
       <c r="Q5" t="n">
         <v>-1.0267</v>
       </c>
       <c r="R5" t="n">
-        <v>1.6427</v>
+        <v>0.616</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1867</v>
+        <v>0.2315</v>
       </c>
       <c r="T5" t="n">
-        <v>0.5965</v>
+        <v>0.5501</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.4098</v>
+        <v>-0.3186</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.1786</v>
+        <v>0.5803</v>
       </c>
       <c r="W5" t="n">
-        <v>0.2402</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.4189</v>
+        <v>0.5803</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>N. FERRER IGLESIA</t>
+          <t>E. COLL COMABELLA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.6985</v>
+        <v>-1.663</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.0026</v>
+        <v>-0.6373</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.6959</v>
+        <v>-1.0257</v>
       </c>
       <c r="G6" t="n">
-        <v>-2.056</v>
+        <v>-1.0984</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.5245</v>
+        <v>-0.2723</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.5314</v>
+        <v>-0.8260999999999999</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.6304999999999999</v>
+        <v>-0.1994</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.0516</v>
+        <v>1.1164</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.579</v>
+        <v>-1.3158</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.4255</v>
+        <v>-0.899</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.473</v>
+        <v>-1.3887</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0475</v>
+        <v>0.4897</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.4107</v>
+        <v>0.616</v>
       </c>
       <c r="Q6" t="n">
         <v>-1.0267</v>
       </c>
       <c r="R6" t="n">
-        <v>0.616</v>
+        <v>1.6427</v>
       </c>
       <c r="S6" t="n">
-        <v>0.1879</v>
+        <v>-0.0019</v>
       </c>
       <c r="T6" t="n">
-        <v>0.6546999999999999</v>
+        <v>0.3486</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.4668</v>
+        <v>-0.3505</v>
       </c>
       <c r="V6" t="n">
-        <v>0.5803</v>
+        <v>-1.1786</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>0.2402</v>
       </c>
       <c r="X6" t="n">
-        <v>0.5803</v>
+        <v>-1.4189</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.0966</v>
+        <v>-2.8707</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1559</v>
+        <v>-0.2625</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.2525</v>
+        <v>-2.6082</v>
       </c>
       <c r="G7" t="n">
         <v>-0.6026</v>
@@ -1000,13 +1000,13 @@
         <v>1.0267</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2821</v>
+        <v>-0.492</v>
       </c>
       <c r="T7" t="n">
-        <v>0.2594</v>
+        <v>-0.159</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0227</v>
+        <v>-0.333</v>
       </c>
       <c r="V7" t="n">
         <v>-2.5975</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>E. KALU</t>
+          <t>J. JUANOLA MADERA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.5362</v>
+        <v>-3.5496</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.5770999999999999</v>
+        <v>-0.6546999999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.9591</v>
+        <v>-2.8949</v>
       </c>
       <c r="G8" t="n">
-        <v>-4.082</v>
+        <v>-3.4997</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.8458</v>
+        <v>-0.3237</v>
       </c>
       <c r="I8" t="n">
-        <v>-2.2361</v>
+        <v>-3.176</v>
       </c>
       <c r="J8" t="n">
-        <v>0.6978</v>
+        <v>1.1928</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.0126</v>
+        <v>2.2591</v>
       </c>
       <c r="L8" t="n">
-        <v>0.7104</v>
+        <v>-1.0663</v>
       </c>
       <c r="M8" t="n">
-        <v>-4.7797</v>
+        <v>-4.6924</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.8332</v>
+        <v>-2.5827</v>
       </c>
       <c r="O8" t="n">
-        <v>-2.9465</v>
+        <v>-2.1097</v>
       </c>
       <c r="P8" t="n">
-        <v>0.4107</v>
+        <v>-2.2588</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.2321</v>
+        <v>-4.3122</v>
       </c>
       <c r="R8" t="n">
-        <v>1.6427</v>
+        <v>2.0534</v>
       </c>
       <c r="S8" t="n">
-        <v>0.3843</v>
+        <v>0.6586</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.283</v>
+        <v>0.3252</v>
       </c>
       <c r="U8" t="n">
-        <v>0.6673</v>
+        <v>0.3334</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.2492</v>
+        <v>1.5503</v>
       </c>
       <c r="W8" t="n">
-        <v>0.2402</v>
+        <v>2.1396</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.4895</v>
+        <v>-0.5893</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. JUANOLA MADERA</t>
+          <t>E. KALU</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.5736</v>
+        <v>-3.9826</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.0343</v>
+        <v>-0.7863</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.5392</v>
+        <v>-3.1963</v>
       </c>
       <c r="G9" t="n">
-        <v>-3.4997</v>
+        <v>-4.082</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.3237</v>
+        <v>-1.8458</v>
       </c>
       <c r="I9" t="n">
-        <v>-3.176</v>
+        <v>-2.2361</v>
       </c>
       <c r="J9" t="n">
-        <v>1.1928</v>
+        <v>0.6978</v>
       </c>
       <c r="K9" t="n">
-        <v>2.2591</v>
+        <v>-0.0126</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.0663</v>
+        <v>0.7104</v>
       </c>
       <c r="M9" t="n">
-        <v>-4.6924</v>
+        <v>-4.7797</v>
       </c>
       <c r="N9" t="n">
-        <v>-2.5827</v>
+        <v>-1.8332</v>
       </c>
       <c r="O9" t="n">
-        <v>-2.1097</v>
+        <v>-2.9465</v>
       </c>
       <c r="P9" t="n">
-        <v>-2.2588</v>
+        <v>0.4107</v>
       </c>
       <c r="Q9" t="n">
-        <v>-4.3122</v>
+        <v>-1.2321</v>
       </c>
       <c r="R9" t="n">
-        <v>2.0534</v>
+        <v>1.6427</v>
       </c>
       <c r="S9" t="n">
-        <v>0.6346000000000001</v>
+        <v>-0.062</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0545</v>
+        <v>-0.4922</v>
       </c>
       <c r="U9" t="n">
-        <v>0.6891</v>
+        <v>0.4302</v>
       </c>
       <c r="V9" t="n">
-        <v>1.5503</v>
+        <v>-0.2492</v>
       </c>
       <c r="W9" t="n">
-        <v>2.1396</v>
+        <v>0.2402</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.5893</v>
+        <v>-0.4895</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.3161</v>
+        <v>-4.6439</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.9996</v>
+        <v>-4.2088</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.3165</v>
+        <v>-0.4351</v>
       </c>
       <c r="G10" t="n">
         <v>-1.888</v>
@@ -1234,13 +1234,13 @@
         <v>1.6427</v>
       </c>
       <c r="S10" t="n">
-        <v>0.2503</v>
+        <v>-0.0775</v>
       </c>
       <c r="T10" t="n">
-        <v>0.457</v>
+        <v>0.2478</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2067</v>
+        <v>-0.3253</v>
       </c>
       <c r="V10" t="n">
         <v>-0.008999999999999999</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.8909</v>
+        <v>-5.4306</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.9949</v>
+        <v>-3.8902</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.8961</v>
+        <v>-1.5404</v>
       </c>
       <c r="G11" t="n">
         <v>-1.6058</v>
@@ -1312,13 +1312,13 @@
         <v>1.8481</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.3088</v>
+        <v>-0.8485</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3334</v>
+        <v>-0.2288</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.9754</v>
+        <v>-0.6197</v>
       </c>
       <c r="V11" t="n">
         <v>1.5412</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-6.492</v>
+        <v>-6.403</v>
       </c>
       <c r="E12" t="n">
         <v>-4.2444</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.2475</v>
+        <v>-2.1586</v>
       </c>
       <c r="G12" t="n">
         <v>-4.8581</v>
@@ -1390,13 +1390,13 @@
         <v>0.2053</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.8125</v>
+        <v>-0.7236</v>
       </c>
       <c r="T12" t="n">
         <v>-0.5851</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2274</v>
+        <v>-0.1385</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-24.9545</v>
+        <v>-24.6252</v>
       </c>
       <c r="E13" t="n">
-        <v>-8.8841</v>
+        <v>-8.554600000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>-16.0705</v>
+        <v>-16.0706</v>
       </c>
       <c r="G13" t="n">
         <v>-16.9972</v>
@@ -1438,7 +1438,7 @@
         <v>-8.6441</v>
       </c>
       <c r="I13" t="n">
-        <v>-8.352600000000001</v>
+        <v>-8.352599999999999</v>
       </c>
       <c r="J13" t="n">
         <v>5.0823</v>
@@ -1447,7 +1447,7 @@
         <v>5.7948</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.7127000000000006</v>
+        <v>-0.7127000000000003</v>
       </c>
       <c r="M13" t="n">
         <v>-22.0791</v>
@@ -1468,16 +1468,16 @@
         <v>13.347</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.9882</v>
+        <v>-0.6587</v>
       </c>
       <c r="T13" t="n">
-        <v>0.8703000000000001</v>
+        <v>1.1996</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.8584</v>
+        <v>-1.8583</v>
       </c>
       <c r="V13" t="n">
-        <v>0.2178</v>
+        <v>0.2177999999999995</v>
       </c>
       <c r="W13" t="n">
         <v>5.697900000000001</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>7.0046</v>
+        <v>7.7577</v>
       </c>
       <c r="E14" t="n">
-        <v>6.0417</v>
+        <v>6.3555</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9629</v>
+        <v>1.4022</v>
       </c>
       <c r="G14" t="n">
         <v>4.461</v>
@@ -1546,13 +1546,13 @@
         <v>2.6694</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.9895</v>
+        <v>-0.2363</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.5928</v>
+        <v>-0.279</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.3966</v>
+        <v>0.0427</v>
       </c>
       <c r="V14" t="n">
         <v>1.8903</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. BADMUS</t>
+          <t>O. BIESHAAR</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>6.918</v>
+        <v>6.1036</v>
       </c>
       <c r="E15" t="n">
-        <v>6.6748</v>
+        <v>3.387</v>
       </c>
       <c r="F15" t="n">
-        <v>0.2432</v>
+        <v>2.7165</v>
       </c>
       <c r="G15" t="n">
-        <v>1.2736</v>
+        <v>4.2861</v>
       </c>
       <c r="H15" t="n">
-        <v>0.1947</v>
+        <v>2.1312</v>
       </c>
       <c r="I15" t="n">
-        <v>1.079</v>
+        <v>2.1549</v>
       </c>
       <c r="J15" t="n">
-        <v>2.3121</v>
+        <v>3.759</v>
       </c>
       <c r="K15" t="n">
-        <v>1.4439</v>
+        <v>1.9305</v>
       </c>
       <c r="L15" t="n">
-        <v>0.8682</v>
+        <v>1.8285</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.0385</v>
+        <v>0.5271</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.2492</v>
+        <v>0.2007</v>
       </c>
       <c r="O15" t="n">
-        <v>0.2107</v>
+        <v>0.3264</v>
       </c>
       <c r="P15" t="n">
-        <v>1.0267</v>
+        <v>1.6427</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-1.0267</v>
       </c>
       <c r="R15" t="n">
-        <v>1.0267</v>
+        <v>2.6694</v>
       </c>
       <c r="S15" t="n">
-        <v>4.2686</v>
+        <v>0.0524</v>
       </c>
       <c r="T15" t="n">
-        <v>3.5331</v>
+        <v>-0.066</v>
       </c>
       <c r="U15" t="n">
-        <v>0.7355</v>
+        <v>0.1183</v>
       </c>
       <c r="V15" t="n">
-        <v>0.3491</v>
+        <v>0.1224</v>
       </c>
       <c r="W15" t="n">
-        <v>0.8295</v>
+        <v>0.7207</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.4805</v>
+        <v>-0.5983000000000001</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>O. BIESHAAR</t>
+          <t>H. FIGUEROA ÁLVAREZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>5.9258</v>
+        <v>5.8159</v>
       </c>
       <c r="E16" t="n">
-        <v>3.4916</v>
+        <v>5.7402</v>
       </c>
       <c r="F16" t="n">
-        <v>2.4342</v>
+        <v>0.0757</v>
       </c>
       <c r="G16" t="n">
-        <v>4.2861</v>
+        <v>4.6447</v>
       </c>
       <c r="H16" t="n">
-        <v>2.1312</v>
+        <v>1.3429</v>
       </c>
       <c r="I16" t="n">
-        <v>2.1549</v>
+        <v>3.3017</v>
       </c>
       <c r="J16" t="n">
-        <v>3.759</v>
+        <v>5.0463</v>
       </c>
       <c r="K16" t="n">
-        <v>1.9305</v>
+        <v>1.5607</v>
       </c>
       <c r="L16" t="n">
-        <v>1.8285</v>
+        <v>3.4857</v>
       </c>
       <c r="M16" t="n">
-        <v>0.5271</v>
+        <v>-0.4017</v>
       </c>
       <c r="N16" t="n">
-        <v>0.2007</v>
+        <v>-0.2177</v>
       </c>
       <c r="O16" t="n">
-        <v>0.3264</v>
+        <v>-0.1839</v>
       </c>
       <c r="P16" t="n">
-        <v>1.6427</v>
+        <v>1.8481</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.0267</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>2.6694</v>
+        <v>1.8481</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.1254</v>
+        <v>0.2616</v>
       </c>
       <c r="T16" t="n">
-        <v>0.0386</v>
+        <v>-0.1357</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.164</v>
+        <v>0.3973</v>
       </c>
       <c r="V16" t="n">
-        <v>0.1224</v>
+        <v>-0.9384</v>
       </c>
       <c r="W16" t="n">
-        <v>0.7207</v>
+        <v>0.8295</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.5983000000000001</v>
+        <v>-1.7679</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>H. FIGUEROA ÁLVAREZ</t>
+          <t>A. BADMUS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>4.6966</v>
+        <v>4.5575</v>
       </c>
       <c r="E17" t="n">
-        <v>5.2172</v>
+        <v>4.3735</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.5205</v>
+        <v>0.1839</v>
       </c>
       <c r="G17" t="n">
-        <v>4.6447</v>
+        <v>1.2736</v>
       </c>
       <c r="H17" t="n">
-        <v>1.3429</v>
+        <v>0.1947</v>
       </c>
       <c r="I17" t="n">
-        <v>3.3017</v>
+        <v>1.079</v>
       </c>
       <c r="J17" t="n">
-        <v>5.0463</v>
+        <v>2.3121</v>
       </c>
       <c r="K17" t="n">
-        <v>1.5607</v>
+        <v>1.4439</v>
       </c>
       <c r="L17" t="n">
-        <v>3.4857</v>
+        <v>0.8682</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.4017</v>
+        <v>-1.0385</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.2177</v>
+        <v>-1.2492</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.1839</v>
+        <v>0.2107</v>
       </c>
       <c r="P17" t="n">
-        <v>1.8481</v>
+        <v>1.0267</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.8481</v>
+        <v>1.0267</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.8577</v>
+        <v>1.9081</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.6587</v>
+        <v>1.2319</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.199</v>
+        <v>0.6762</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.9384</v>
+        <v>0.3491</v>
       </c>
       <c r="W17" t="n">
         <v>0.8295</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.7679</v>
+        <v>-0.4805</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.8082</v>
+        <v>4.1506</v>
       </c>
       <c r="E18" t="n">
-        <v>3.6449</v>
+        <v>4.2725</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.8367</v>
+        <v>-0.1219</v>
       </c>
       <c r="G18" t="n">
         <v>4.8895</v>
@@ -1858,13 +1858,13 @@
         <v>1.6427</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.5187</v>
+        <v>-0.1763</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.7905</v>
+        <v>-0.1628</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.7282999999999999</v>
+        <v>-0.0134</v>
       </c>
       <c r="V18" t="n">
         <v>-1.1786</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>2.0349</v>
+        <v>2.1238</v>
       </c>
       <c r="E19" t="n">
-        <v>0.5622</v>
+        <v>0.1437</v>
       </c>
       <c r="F19" t="n">
-        <v>1.4728</v>
+        <v>1.9801</v>
       </c>
       <c r="G19" t="n">
         <v>1.255</v>
@@ -1936,13 +1936,13 @@
         <v>2.0534</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.0066</v>
+        <v>0.0823</v>
       </c>
       <c r="T19" t="n">
-        <v>0.6042</v>
+        <v>0.1858</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.6108</v>
+        <v>-0.1035</v>
       </c>
       <c r="V19" t="n">
         <v>-0.2402</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>P. LOPEZ-SANVICENTE RETA</t>
+          <t>A. SMITH</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.1353</v>
+        <v>0.3178</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.827</v>
+        <v>-0.7073</v>
       </c>
       <c r="F20" t="n">
-        <v>1.9623</v>
+        <v>1.0251</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.6845</v>
+        <v>-1.007</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.237</v>
+        <v>-1.291</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.4475</v>
+        <v>0.2839</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.3434</v>
+        <v>0.2997</v>
       </c>
       <c r="K20" t="n">
-        <v>0.3149</v>
+        <v>0.458</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.6583</v>
+        <v>-0.1582</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.3411</v>
+        <v>-1.3068</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.5518999999999999</v>
+        <v>-1.7489</v>
       </c>
       <c r="O20" t="n">
-        <v>0.2107</v>
+        <v>0.4422</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.4107</v>
+        <v>-0</v>
       </c>
       <c r="Q20" t="n">
         <v>-2.0534</v>
       </c>
       <c r="R20" t="n">
-        <v>1.6427</v>
+        <v>2.0534</v>
       </c>
       <c r="S20" t="n">
-        <v>0.6412</v>
+        <v>0.3729</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.0195</v>
+        <v>-0.0234</v>
       </c>
       <c r="U20" t="n">
-        <v>0.6607</v>
+        <v>0.3962</v>
       </c>
       <c r="V20" t="n">
-        <v>0.5893</v>
+        <v>0.9519</v>
       </c>
       <c r="W20" t="n">
-        <v>0.5893</v>
+        <v>1.0698</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-0.1179</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. SMITH</t>
+          <t>P. LOPEZ-SANVICENTE RETA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.6986</v>
+        <v>0.2312</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.3349</v>
+        <v>-1.7224</v>
       </c>
       <c r="F21" t="n">
-        <v>0.6363</v>
+        <v>1.9536</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.007</v>
+        <v>-0.6845</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.291</v>
+        <v>-0.237</v>
       </c>
       <c r="I21" t="n">
-        <v>0.2839</v>
+        <v>-0.4475</v>
       </c>
       <c r="J21" t="n">
-        <v>0.2997</v>
+        <v>-0.3434</v>
       </c>
       <c r="K21" t="n">
-        <v>0.458</v>
+        <v>0.3149</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.1582</v>
+        <v>-0.6583</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.3068</v>
+        <v>-0.3411</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.7489</v>
+        <v>-0.5518999999999999</v>
       </c>
       <c r="O21" t="n">
-        <v>0.4422</v>
+        <v>0.2107</v>
       </c>
       <c r="P21" t="n">
-        <v>-0</v>
+        <v>-0.4107</v>
       </c>
       <c r="Q21" t="n">
         <v>-2.0534</v>
       </c>
       <c r="R21" t="n">
-        <v>2.0534</v>
+        <v>1.6427</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.6435</v>
+        <v>0.7371</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.651</v>
+        <v>0.0851</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0075</v>
+        <v>0.652</v>
       </c>
       <c r="V21" t="n">
-        <v>0.9519</v>
+        <v>0.5893</v>
       </c>
       <c r="W21" t="n">
-        <v>1.0698</v>
+        <v>0.5893</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.1179</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.7701</v>
+        <v>0.2045</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.9022</v>
+        <v>-0.6929999999999999</v>
       </c>
       <c r="F22" t="n">
-        <v>0.1321</v>
+        <v>0.8975</v>
       </c>
       <c r="G22" t="n">
         <v>-1.2826</v>
@@ -2170,13 +2170,13 @@
         <v>1.0267</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.3964</v>
+        <v>0.5782</v>
       </c>
       <c r="T22" t="n">
-        <v>0.3757</v>
+        <v>0.5849</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.7721</v>
+        <v>-0.0067</v>
       </c>
       <c r="V22" t="n">
         <v>-0.1179</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.9157</v>
+        <v>-0.4554</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.0785</v>
+        <v>-2.3923</v>
       </c>
       <c r="F23" t="n">
-        <v>1.1628</v>
+        <v>1.9369</v>
       </c>
       <c r="G23" t="n">
         <v>0.2325</v>
@@ -2248,13 +2248,13 @@
         <v>2.6694</v>
       </c>
       <c r="S23" t="n">
-        <v>0.2099</v>
+        <v>0.6702</v>
       </c>
       <c r="T23" t="n">
-        <v>0.7437</v>
+        <v>0.4299</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.5338000000000001</v>
+        <v>0.2403</v>
       </c>
       <c r="V23" t="n">
         <v>-0.9474</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.1846</v>
+        <v>-1.6686</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.4192</v>
+        <v>-2.687</v>
       </c>
       <c r="F24" t="n">
-        <v>1.2346</v>
+        <v>1.0184</v>
       </c>
       <c r="G24" t="n">
         <v>-1.0712</v>
@@ -2326,13 +2326,13 @@
         <v>1.2321</v>
       </c>
       <c r="S24" t="n">
-        <v>0.4061</v>
+        <v>0.9221</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.7246</v>
+        <v>0.0076</v>
       </c>
       <c r="U24" t="n">
-        <v>1.1307</v>
+        <v>0.9145</v>
       </c>
       <c r="V24" t="n">
         <v>-0.6982</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>24.9544</v>
+        <v>29.1386</v>
       </c>
       <c r="E25" t="n">
-        <v>16.0706</v>
+        <v>16.0704</v>
       </c>
       <c r="F25" t="n">
-        <v>8.884</v>
+        <v>13.068</v>
       </c>
       <c r="G25" t="n">
         <v>16.9971</v>
@@ -2389,7 +2389,7 @@
         <v>-5.0821</v>
       </c>
       <c r="N25" t="n">
-        <v>-5.7946</v>
+        <v>-5.794600000000001</v>
       </c>
       <c r="O25" t="n">
         <v>0.7126000000000002</v>
@@ -2404,13 +2404,13 @@
         <v>20.534</v>
       </c>
       <c r="S25" t="n">
-        <v>0.9880000000000004</v>
+        <v>5.1723</v>
       </c>
       <c r="T25" t="n">
-        <v>1.8582</v>
+        <v>1.8583</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.8702000000000001</v>
+        <v>3.3139</v>
       </c>
       <c r="V25" t="n">
         <v>-0.2176999999999999</v>
